--- a/data/trans_orig/P3A_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P3A_R-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>28418</t>
+          <t>28455</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>44297</t>
+          <t>44130</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,82 +748,82 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>27,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
+          <t>41,95%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>45654</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>37432</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>54401</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>38,6%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>31,64%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>45,99%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>81538</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>69541</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>94088</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>36,48%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>31,11%</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
           <t>42,1%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>45654</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>36877</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>54208</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>38,6%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>31,18%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>45,83%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>81538</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>70536</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>93133</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>36,48%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>31,56%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>41,67%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>60912</t>
+          <t>61079</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>76791</t>
+          <t>76754</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,82 +861,82 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
+          <t>58,05%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>72,95%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>72635</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>63888</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>80857</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>61,4%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>54,01%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>68,36%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>141961</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>129411</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>153958</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>63,52%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
           <t>57,9%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>72,99%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>72635</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>64081</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>81412</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>61,4%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>54,17%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>68,82%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>204</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>141961</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>130366</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>152963</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>63,52%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>58,33%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>68,44%</t>
+          <t>68,89%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>39870</t>
+          <t>39453</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>56767</t>
+          <t>57170</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>31,57%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>45,43%</t>
+          <t>45,75%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>43444</t>
+          <t>43409</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>61925</t>
+          <t>61607</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>44,0%</t>
+          <t>43,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>87780</t>
+          <t>87139</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>112738</t>
+          <t>113619</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>33,04%</t>
+          <t>32,8%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>42,43%</t>
+          <t>42,76%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>68198</t>
+          <t>67795</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>85095</t>
+          <t>85512</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>54,57%</t>
+          <t>54,25%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>68,1%</t>
+          <t>68,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>78817</t>
+          <t>79135</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>97298</t>
+          <t>97333</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>56,0%</t>
+          <t>56,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>69,13%</t>
+          <t>69,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>152969</t>
+          <t>152088</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>177927</t>
+          <t>178568</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>57,57%</t>
+          <t>57,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>66,96%</t>
+          <t>67,2%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>29489</t>
+          <t>30117</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>44844</t>
+          <t>44402</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>27,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>41,58%</t>
+          <t>41,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>30858</t>
+          <t>30341</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>48023</t>
+          <t>46832</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>42,66%</t>
+          <t>41,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>65309</t>
+          <t>65279</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>88640</t>
+          <t>87432</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>29,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>40,21%</t>
+          <t>39,67%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>63004</t>
+          <t>63446</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>78359</t>
+          <t>77731</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>58,42%</t>
+          <t>58,83%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>72,66%</t>
+          <t>72,07%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>64550</t>
+          <t>65741</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>81715</t>
+          <t>82232</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>57,34%</t>
+          <t>58,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>72,59%</t>
+          <t>73,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>131780</t>
+          <t>132988</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>155111</t>
+          <t>155141</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>59,79%</t>
+          <t>60,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>70,37%</t>
+          <t>70,38%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>46511</t>
+          <t>46693</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>67433</t>
+          <t>68002</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>40,79%</t>
+          <t>41,13%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>43438</t>
+          <t>43155</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>62585</t>
+          <t>62350</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>39,88%</t>
+          <t>39,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>93465</t>
+          <t>94647</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>122607</t>
+          <t>123073</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,04%</t>
+          <t>38,19%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>97903</t>
+          <t>97334</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>118825</t>
+          <t>118643</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>59,21%</t>
+          <t>58,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>71,87%</t>
+          <t>71,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>94361</t>
+          <t>94596</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>113508</t>
+          <t>113791</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>60,12%</t>
+          <t>60,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,32%</t>
+          <t>72,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>199675</t>
+          <t>199209</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>228817</t>
+          <t>227635</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>61,96%</t>
+          <t>61,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,0%</t>
+          <t>70,63%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>160825</t>
+          <t>161434</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>194731</t>
+          <t>195904</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>32,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>38,69%</t>
+          <t>38,92%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>172522</t>
+          <t>170832</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>206363</t>
+          <t>207188</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>39,04%</t>
+          <t>39,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>344083</t>
+          <t>343708</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>397200</t>
+          <t>389694</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>33,34%</t>
+          <t>33,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>38,49%</t>
+          <t>37,76%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>308628</t>
+          <t>307455</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>342534</t>
+          <t>341925</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>61,31%</t>
+          <t>61,08%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>68,05%</t>
+          <t>67,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>322186</t>
+          <t>321361</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>356027</t>
+          <t>357717</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>60,96%</t>
+          <t>60,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>67,36%</t>
+          <t>67,68%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>634708</t>
+          <t>642214</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>687825</t>
+          <t>688200</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>61,51%</t>
+          <t>62,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>66,66%</t>
+          <t>66,69%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>29999</t>
+          <t>29497</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>46293</t>
+          <t>45067</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>30,89%</t>
+          <t>30,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>47,66%</t>
+          <t>46,4%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>33854</t>
+          <t>34239</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>50839</t>
+          <t>51342</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>45,19%</t>
+          <t>45,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>68434</t>
+          <t>68016</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>91465</t>
+          <t>91665</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,65%</t>
+          <t>32,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>43,63%</t>
+          <t>43,73%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>50836</t>
+          <t>52062</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>67130</t>
+          <t>67632</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>52,34%</t>
+          <t>53,6%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>69,11%</t>
+          <t>69,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>61662</t>
+          <t>61159</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>78647</t>
+          <t>78262</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>54,81%</t>
+          <t>54,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>69,91%</t>
+          <t>69,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>118164</t>
+          <t>117964</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>141195</t>
+          <t>141613</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>56,37%</t>
+          <t>56,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>67,35%</t>
+          <t>67,55%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>39455</t>
+          <t>39838</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>56676</t>
+          <t>57250</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>30,89%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>43,94%</t>
+          <t>44,39%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>45181</t>
+          <t>44698</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>65411</t>
+          <t>63983</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>42,32%</t>
+          <t>41,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>89171</t>
+          <t>89551</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>114215</t>
+          <t>115368</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>31,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>40,28%</t>
+          <t>40,69%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>72307</t>
+          <t>71733</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>89528</t>
+          <t>89145</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>56,06%</t>
+          <t>55,61%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>69,41%</t>
+          <t>69,11%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>89145</t>
+          <t>90573</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>109375</t>
+          <t>109858</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>57,68%</t>
+          <t>58,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>70,77%</t>
+          <t>71,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>169324</t>
+          <t>168171</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>194368</t>
+          <t>193988</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>59,72%</t>
+          <t>59,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>68,55%</t>
+          <t>68,42%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>26912</t>
+          <t>27309</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>42574</t>
+          <t>42742</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>40,6%</t>
+          <t>40,76%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>34752</t>
+          <t>34477</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>51249</t>
+          <t>50357</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>29,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>43,88%</t>
+          <t>43,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>65850</t>
+          <t>65377</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>88021</t>
+          <t>88085</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>39,71%</t>
+          <t>39,74%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>62277</t>
+          <t>62109</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>77939</t>
+          <t>77542</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>59,4%</t>
+          <t>59,24%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>74,33%</t>
+          <t>73,95%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>65535</t>
+          <t>66427</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>82032</t>
+          <t>82307</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>56,12%</t>
+          <t>56,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>70,24%</t>
+          <t>70,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>133613</t>
+          <t>133549</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>155784</t>
+          <t>156257</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>60,29%</t>
+          <t>60,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>70,29%</t>
+          <t>70,5%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>35490</t>
+          <t>35659</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>55297</t>
+          <t>54409</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>37,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>34094</t>
+          <t>34404</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>53431</t>
+          <t>53389</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>34,48%</t>
+          <t>34,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>74815</t>
+          <t>75299</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>101533</t>
+          <t>102175</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>33,95%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>90705</t>
+          <t>91593</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>110512</t>
+          <t>110343</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>62,13%</t>
+          <t>62,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>75,69%</t>
+          <t>75,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>101510</t>
+          <t>101552</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>120847</t>
+          <t>120537</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>65,52%</t>
+          <t>65,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>78,0%</t>
+          <t>77,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>199410</t>
+          <t>198768</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>226128</t>
+          <t>225644</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,26%</t>
+          <t>66,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,14%</t>
+          <t>74,98%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>146023</t>
+          <t>148578</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>180617</t>
+          <t>181319</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>38,02%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>163677</t>
+          <t>165504</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>200904</t>
+          <t>202389</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>37,29%</t>
+          <t>37,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>322566</t>
+          <t>323044</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>370197</t>
+          <t>373546</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>31,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
+          <t>36,78%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>296348</t>
+          <t>295646</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>330942</t>
+          <t>328387</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>62,13%</t>
+          <t>61,98%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>69,39%</t>
+          <t>68,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>337877</t>
+          <t>336392</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>375104</t>
+          <t>373277</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>62,71%</t>
+          <t>62,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>69,62%</t>
+          <t>69,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>645549</t>
+          <t>642200</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>693180</t>
+          <t>692702</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>63,55%</t>
+          <t>63,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>68,24%</t>
+          <t>68,2%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18900</t>
+          <t>18253</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>33699</t>
+          <t>32587</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>37,41%</t>
+          <t>36,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>26071</t>
+          <t>26591</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>43165</t>
+          <t>43040</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,24%</t>
+          <t>41,12%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>48407</t>
+          <t>49839</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>70572</t>
+          <t>71815</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,24%</t>
+          <t>36,87%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>56386</t>
+          <t>57498</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>71185</t>
+          <t>71832</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>62,59%</t>
+          <t>63,83%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>79,02%</t>
+          <t>79,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>61509</t>
+          <t>61634</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>78603</t>
+          <t>78083</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>58,76%</t>
+          <t>58,88%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>75,09%</t>
+          <t>74,6%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>124187</t>
+          <t>122944</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>146352</t>
+          <t>144920</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>63,76%</t>
+          <t>63,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>75,15%</t>
+          <t>74,41%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>39792</t>
+          <t>39536</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>57378</t>
+          <t>57291</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>26,02%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,77%</t>
+          <t>37,71%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>44144</t>
+          <t>43607</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>63861</t>
+          <t>62996</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>35,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>87331</t>
+          <t>87329</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>114187</t>
+          <t>115944</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5060,7 +5060,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>35,43%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>94549</t>
+          <t>94636</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>112135</t>
+          <t>112391</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>62,23%</t>
+          <t>62,29%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>73,81%</t>
+          <t>73,98%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>111442</t>
+          <t>112307</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>131159</t>
+          <t>131696</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>63,57%</t>
+          <t>64,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>74,82%</t>
+          <t>75,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>213043</t>
+          <t>211286</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>239899</t>
+          <t>239901</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,7 +5168,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>65,1%</t>
+          <t>64,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>31977</t>
+          <t>31178</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>47450</t>
+          <t>47031</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>40,71%</t>
+          <t>40,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>39609</t>
+          <t>40131</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>57707</t>
+          <t>58334</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>29,82%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>43,44%</t>
+          <t>43,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>75732</t>
+          <t>76543</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>100127</t>
+          <t>99679</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>40,15%</t>
+          <t>39,97%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>69102</t>
+          <t>69521</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>84575</t>
+          <t>85374</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>59,29%</t>
+          <t>59,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>72,56%</t>
+          <t>73,25%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>75140</t>
+          <t>74513</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>93238</t>
+          <t>92716</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>56,56%</t>
+          <t>56,09%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>70,18%</t>
+          <t>69,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>149272</t>
+          <t>149720</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>173667</t>
+          <t>172856</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>59,85%</t>
+          <t>60,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>69,63%</t>
+          <t>69,31%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>48348</t>
+          <t>48282</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>69671</t>
+          <t>68851</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>28,94%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>41,76%</t>
+          <t>41,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>44133</t>
+          <t>42730</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>62706</t>
+          <t>62308</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>27,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>39,64%</t>
+          <t>39,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>97548</t>
+          <t>97887</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>125784</t>
+          <t>125643</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,7%</t>
+          <t>38,66%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>97156</t>
+          <t>97976</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>118479</t>
+          <t>118545</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>58,24%</t>
+          <t>58,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>71,02%</t>
+          <t>71,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>95502</t>
+          <t>95900</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>114075</t>
+          <t>115478</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>60,36%</t>
+          <t>60,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,1%</t>
+          <t>72,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>199251</t>
+          <t>199392</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>227487</t>
+          <t>227148</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>61,3%</t>
+          <t>61,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,99%</t>
+          <t>69,88%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>152738</t>
+          <t>154519</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>189092</t>
+          <t>189234</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>29,41%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>35,99%</t>
+          <t>36,02%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>171826</t>
+          <t>171223</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>209631</t>
+          <t>207722</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>29,98%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>36,71%</t>
+          <t>36,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>333531</t>
+          <t>334332</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>387098</t>
+          <t>382916</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>30,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>35,31%</t>
+          <t>34,92%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>336298</t>
+          <t>336156</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>372652</t>
+          <t>370871</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>64,01%</t>
+          <t>63,98%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>70,93%</t>
+          <t>70,59%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>361402</t>
+          <t>363311</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>399207</t>
+          <t>399810</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>63,29%</t>
+          <t>63,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>69,91%</t>
+          <t>70,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>709325</t>
+          <t>713507</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>762892</t>
+          <t>762091</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>64,69%</t>
+          <t>65,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,58%</t>
+          <t>69,51%</t>
         </is>
       </c>
     </row>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>99195</t>
+          <t>98534</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>109154</t>
+          <t>109496</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>84,58%</t>
+          <t>84,02%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>122764</t>
+          <t>122534</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>134523</t>
+          <t>134651</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>87,43%</t>
+          <t>87,27%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>225290</t>
+          <t>225502</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>241295</t>
+          <t>241625</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>87,43%</t>
+          <t>87,51%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,76%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8126</t>
+          <t>7784</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18085</t>
+          <t>18746</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5889</t>
+          <t>5761</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17648</t>
+          <t>17878</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>16398</t>
+          <t>16068</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>32403</t>
+          <t>32191</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,49%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>144219</t>
+          <t>144370</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>170577</t>
+          <t>170818</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>75,7%</t>
+          <t>75,78%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>89,54%</t>
+          <t>89,66%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>199467</t>
+          <t>199003</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>222449</t>
+          <t>221945</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>78,21%</t>
+          <t>78,03%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>87,22%</t>
+          <t>87,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>353093</t>
+          <t>353384</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>387626</t>
+          <t>389102</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>79,25%</t>
+          <t>79,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>87,0%</t>
+          <t>87,33%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>19935</t>
+          <t>19694</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>46293</t>
+          <t>46142</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>32586</t>
+          <t>33090</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>55568</t>
+          <t>56032</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>57922</t>
+          <t>56446</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>92455</t>
+          <t>92164</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,69%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>159720</t>
+          <t>158788</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>178871</t>
+          <t>179542</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>83,89%</t>
+          <t>83,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>151093</t>
+          <t>151654</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>169225</t>
+          <t>168248</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>81,55%</t>
+          <t>81,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>90,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>318947</t>
+          <t>318088</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>344280</t>
+          <t>344343</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>84,9%</t>
+          <t>84,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>91,66%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11530</t>
+          <t>10859</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>30681</t>
+          <t>31613</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>16061</t>
+          <t>17038</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>34193</t>
+          <t>33632</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>31407</t>
+          <t>31344</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>56740</t>
+          <t>57599</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>15,33%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>124292</t>
+          <t>124909</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>143048</t>
+          <t>143132</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>74,0%</t>
+          <t>74,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>85,17%</t>
+          <t>85,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>144001</t>
+          <t>143591</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>161458</t>
+          <t>161390</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>79,45%</t>
+          <t>79,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>89,09%</t>
+          <t>89,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>275155</t>
+          <t>275701</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>300207</t>
+          <t>300775</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>78,8%</t>
+          <t>78,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>85,97%</t>
+          <t>86,13%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>24914</t>
+          <t>24830</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>43670</t>
+          <t>43053</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>25,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>19780</t>
+          <t>19848</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>37237</t>
+          <t>37647</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>48994</t>
+          <t>48426</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>74046</t>
+          <t>73500</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>21,05%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>548406</t>
+          <t>549921</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>588993</t>
+          <t>590002</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>82,32%</t>
+          <t>82,55%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>88,57%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>637741</t>
+          <t>637030</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>674181</t>
+          <t>673605</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>83,7%</t>
+          <t>83,6%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>88,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1198846</t>
+          <t>1200986</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1254226</t>
+          <t>1252460</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>83,95%</t>
+          <t>84,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>87,7%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>77162</t>
+          <t>76153</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>117749</t>
+          <t>116234</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>87791</t>
+          <t>88367</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>124231</t>
+          <t>124942</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>173901</t>
+          <t>175667</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>229281</t>
+          <t>227141</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>15,9%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P3A_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P3A_R-Habitat-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>45654</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>37390</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>55693</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>38,6%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>31,61%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>47,08%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>35883</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>28455</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>44130</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>27514</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>43883</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>34,11%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>27,05%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>41,95%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>45654</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>37432</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>54401</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>38,6%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>45,99%</t>
+          <t>41,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>69541</t>
+          <t>70067</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>94088</t>
+          <t>93625</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>31,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,1%</t>
+          <t>41,89%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>72635</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>62596</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>80899</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>61,4%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>52,92%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>68,39%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>69326</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>61079</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>76754</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>61326</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>77695</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>65,89%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>58,05%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>72,95%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>72635</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>63888</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>80857</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>61,4%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>54,01%</t>
+          <t>58,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>68,36%</t>
+          <t>73,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>129411</t>
+          <t>129874</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>153958</t>
+          <t>153432</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>57,9%</t>
+          <t>58,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>68,89%</t>
+          <t>68,65%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>118289</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>118289</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>118289</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>105209</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>105209</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>105209</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>172</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>118289</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>118289</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>118289</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>52336</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>43519</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>61363</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>37,19%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>30,92%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>43,6%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>77</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>48145</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>39453</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>57170</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>39680</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>57095</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>38,53%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>31,57%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>45,75%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>52336</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>43409</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>61607</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>37,19%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>31,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>43,77%</t>
+          <t>45,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>87139</t>
+          <t>87923</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>113619</t>
+          <t>113251</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>32,8%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>42,76%</t>
+          <t>42,62%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>88406</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>79379</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>97223</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>62,81%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>56,4%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>69,08%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>124</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>76820</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>67795</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>85512</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>67870</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>85285</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>61,47%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>54,25%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>68,43%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>136</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>88406</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>79135</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>97333</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>62,81%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>56,23%</t>
+          <t>54,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>69,16%</t>
+          <t>68,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>152088</t>
+          <t>152456</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>178568</t>
+          <t>177784</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>57,24%</t>
+          <t>57,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>67,2%</t>
+          <t>66,91%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>140742</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>140742</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>140742</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>201</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>124965</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>124965</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>124965</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>216</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>140742</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>140742</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>140742</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>38509</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>30326</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>47212</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>34,21%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>26,94%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>41,94%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>37339</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>30117</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>44402</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>29460</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>45670</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>34,62%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>27,93%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>41,17%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>38509</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>30341</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>46832</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>34,21%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>41,6%</t>
+          <t>42,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>65279</t>
+          <t>64889</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>87432</t>
+          <t>86632</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>29,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>39,67%</t>
+          <t>39,3%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>74064</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>65361</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>82247</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>65,79%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>58,06%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>73,06%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>115</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>70509</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>63446</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>77731</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>62178</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>78388</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>65,38%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>58,83%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>72,07%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>74064</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>65741</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>82232</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>65,79%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>58,4%</t>
+          <t>57,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>73,05%</t>
+          <t>72,68%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>132988</t>
+          <t>133788</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>155141</t>
+          <t>155531</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>60,33%</t>
+          <t>60,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>70,38%</t>
+          <t>70,56%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>112573</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>112573</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>112573</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>177</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>107848</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>107848</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>107848</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>173</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>112573</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>112573</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>112573</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>52184</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>42985</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>62852</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>33,25%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>27,39%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>40,05%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>73</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>56671</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>46693</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>68002</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>45960</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>67518</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>34,28%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>28,24%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>41,13%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>52184</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>43155</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>62350</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>33,25%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>39,73%</t>
+          <t>40,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>94647</t>
+          <t>94322</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>123073</t>
+          <t>122197</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,19%</t>
+          <t>37,92%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>104762</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>94094</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>113961</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>66,75%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>59,95%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>72,61%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>143</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>108665</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>97334</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>118643</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>97818</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>119376</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>65,72%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>58,87%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>71,76%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>154</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>104762</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>94596</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>113791</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>66,75%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>60,27%</t>
+          <t>59,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,5%</t>
+          <t>72,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>199209</t>
+          <t>200085</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>227635</t>
+          <t>227960</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>61,81%</t>
+          <t>62,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>70,63%</t>
+          <t>70,73%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>156946</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>156946</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>156946</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>216</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>165336</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>165336</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>165336</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>231</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>156946</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>156946</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>156946</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,72 +2095,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>284</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>188683</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>172022</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>207056</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>35,7%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>32,55%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>39,17%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>264</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>178038</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>161434</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>195904</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>160422</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>195426</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>35,37%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>32,07%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>38,92%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>284</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>188683</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>170832</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>207188</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>35,7%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>32,32%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>39,2%</t>
+          <t>38,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>343708</t>
+          <t>343940</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>389694</t>
+          <t>392042</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>33,31%</t>
+          <t>33,33%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>37,76%</t>
+          <t>37,99%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>508</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>339866</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>321493</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>356527</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>64,3%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>60,83%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>67,45%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>482</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>325321</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>307455</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>341925</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>307933</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>342937</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>64,63%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>61,08%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>67,93%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>508</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>339866</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>321361</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>357717</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>64,3%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>60,8%</t>
+          <t>61,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>67,68%</t>
+          <t>68,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>642214</t>
+          <t>639866</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>688200</t>
+          <t>687968</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>62,24%</t>
+          <t>62,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>66,69%</t>
+          <t>66,67%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>792</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>746</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>503359</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>503359</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>503359</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>792</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,72 +2670,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>42255</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>34752</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>52362</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>37,56%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>30,89%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>46,54%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>37204</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>29497</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>45067</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>29663</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>45220</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>38,3%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>30,37%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>46,4%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>42255</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>34239</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>51342</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>37,56%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>30,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>45,64%</t>
+          <t>46,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>68016</t>
+          <t>68674</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>91665</t>
+          <t>92051</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,45%</t>
+          <t>32,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>43,73%</t>
+          <t>43,91%</t>
         </is>
       </c>
     </row>
@@ -2783,72 +2783,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>70246</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>60139</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>77749</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>62,44%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>53,46%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>69,11%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>82</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>59925</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>52062</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>67632</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>51909</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>67466</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>61,7%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>53,6%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>69,63%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>70246</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>61159</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>78262</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>62,44%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>54,36%</t>
+          <t>53,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>69,57%</t>
+          <t>69,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>117964</t>
+          <t>117578</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>141613</t>
+          <t>140955</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>56,27%</t>
+          <t>56,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>67,55%</t>
+          <t>67,24%</t>
         </is>
       </c>
     </row>
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>112501</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>112501</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>112501</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>133</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>97129</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>97129</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>97129</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>156</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>112501</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>112501</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>112501</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>53896</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>45061</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>63984</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>34,87%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>29,16%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>41,4%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>48089</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>39838</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>57250</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>39493</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>57682</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>37,28%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>30,89%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>44,39%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>53896</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>44698</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>63983</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>34,87%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>30,62%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,4%</t>
+          <t>44,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>89551</t>
+          <t>88638</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>115368</t>
+          <t>114677</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>40,69%</t>
+          <t>40,44%</t>
         </is>
       </c>
     </row>
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>100660</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>90572</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>109495</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>65,13%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>58,6%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>70,84%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>124</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>80894</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>71733</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>89145</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>71301</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>89490</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>62,72%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>55,61%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>69,11%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>144</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>100660</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>90573</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>109858</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>65,13%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>58,6%</t>
+          <t>55,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>71,08%</t>
+          <t>69,38%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>168171</t>
+          <t>168862</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>193988</t>
+          <t>194901</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>59,31%</t>
+          <t>59,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>68,42%</t>
+          <t>68,74%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>154556</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>154556</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>154556</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>199</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>128983</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>128983</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>128983</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>154556</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>154556</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>154556</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,72 +3356,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>42129</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>34016</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>50940</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>36,07%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>29,13%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>43,62%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>34300</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>27309</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>42742</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>26516</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>42608</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>32,71%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>26,05%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>40,76%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>42129</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>34477</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>50357</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>36,07%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>43,12%</t>
+          <t>40,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>65377</t>
+          <t>64139</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>88085</t>
+          <t>88310</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>28,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>39,74%</t>
+          <t>39,84%</t>
         </is>
       </c>
     </row>
@@ -3469,72 +3469,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>74655</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>65844</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>82768</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>63,93%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>56,38%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>70,87%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>111</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>70551</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>62109</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>77542</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>62243</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>78335</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>67,29%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>59,24%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>73,95%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>74655</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>66427</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>82307</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>63,93%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>56,88%</t>
+          <t>59,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>70,48%</t>
+          <t>74,71%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>133549</t>
+          <t>133324</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>156257</t>
+          <t>157495</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>60,26%</t>
+          <t>60,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>70,5%</t>
+          <t>71,06%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>116784</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>116784</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>116784</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>164</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>104851</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>104851</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>104851</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>116784</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>116784</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>116784</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3704,67 +3704,67 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>43585</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>34475</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>54790</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>28,13%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>22,25%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>35,36%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
           <t>44342</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>35659</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>54409</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>35375</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>54435</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>30,37%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>24,42%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>37,27%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>43585</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>34404</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>53389</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>28,13%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>34,46%</t>
+          <t>37,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>75299</t>
+          <t>75396</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>102175</t>
+          <t>102472</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,95%</t>
+          <t>34,05%</t>
         </is>
       </c>
     </row>
@@ -3812,72 +3812,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>111356</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>100151</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>120466</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>71,87%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>64,64%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>77,75%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>133</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>101660</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>91593</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>110343</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>91567</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>110627</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>69,63%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>62,73%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>75,58%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>154</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>111356</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>101552</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>120537</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>71,87%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>65,54%</t>
+          <t>62,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,8%</t>
+          <t>75,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>198768</t>
+          <t>198471</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>225644</t>
+          <t>225547</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,05%</t>
+          <t>65,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>74,98%</t>
+          <t>74,95%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>154941</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>154941</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>154941</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>191</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>146002</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>146002</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>146002</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>154941</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>154941</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>154941</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>181865</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>162166</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>200479</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>33,75%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>30,1%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>37,21%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>237</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>163934</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>148578</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>181319</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>147102</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>181161</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>34,37%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>31,15%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>38,02%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>258</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>181865</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>165504</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>202389</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>33,75%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>37,56%</t>
+          <t>37,98%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>323044</t>
+          <t>322120</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>373546</t>
+          <t>370964</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>31,8%</t>
+          <t>31,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>36,78%</t>
+          <t>36,52%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>356916</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>338302</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>376615</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>66,25%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>62,79%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>69,9%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>450</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>313031</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>295646</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>328387</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>295804</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>329863</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>65,63%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>61,98%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>68,85%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>511</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>356916</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>336392</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>373277</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>66,25%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>62,44%</t>
+          <t>62,02%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>69,28%</t>
+          <t>69,16%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>642200</t>
+          <t>644782</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>692702</t>
+          <t>693626</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>63,22%</t>
+          <t>63,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>68,2%</t>
+          <t>68,29%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>769</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>538781</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>538781</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>538781</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>687</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>476965</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>476965</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>476965</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>769</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>538781</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>538781</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>538781</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4617,72 +4617,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>33996</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>26062</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>42905</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>32,48%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>24,9%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>40,99%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>25437</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>18253</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>32587</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>18964</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>33178</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>28,24%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>20,26%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>36,17%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>33996</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>26591</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>43040</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>32,48%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,12%</t>
+          <t>36,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>49839</t>
+          <t>48236</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>71815</t>
+          <t>70317</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,87%</t>
+          <t>36,1%</t>
         </is>
       </c>
     </row>
@@ -4730,72 +4730,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>70678</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>61769</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>78612</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>67,52%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>59,01%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>75,1%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>91</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>64648</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>57498</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>71832</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>56907</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>71121</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>71,76%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>63,83%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>79,74%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>70678</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>61634</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>78083</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>67,52%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>58,88%</t>
+          <t>63,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>74,6%</t>
+          <t>78,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>122944</t>
+          <t>124442</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>144920</t>
+          <t>146523</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>63,13%</t>
+          <t>63,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>74,41%</t>
+          <t>75,23%</t>
         </is>
       </c>
     </row>
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>104674</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>104674</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>104674</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>126</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>90085</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>90085</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>90085</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>104674</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>104674</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>104674</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,72 +4960,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>52975</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>43099</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>63202</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>30,22%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>24,59%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>36,05%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>76</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>48150</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>39536</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>57291</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>39295</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>57223</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>31,69%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>26,02%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>37,71%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>52975</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>43607</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>62996</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>30,22%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>35,94%</t>
+          <t>37,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>87329</t>
+          <t>89607</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>115944</t>
+          <t>114917</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,43%</t>
+          <t>35,12%</t>
         </is>
       </c>
     </row>
@@ -5073,72 +5073,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>122328</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>112101</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>132204</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>69,78%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>63,95%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>75,41%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>169</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>103777</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>94636</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>112391</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>94704</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>112632</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>68,31%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>62,29%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>73,98%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>185</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>122328</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>112307</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>131696</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>69,78%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>64,06%</t>
+          <t>62,34%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>75,12%</t>
+          <t>74,14%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>211286</t>
+          <t>212313</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>239901</t>
+          <t>237623</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>64,57%</t>
+          <t>64,88%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>73,31%</t>
+          <t>72,62%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>175303</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>175303</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>175303</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>245</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>151927</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>151927</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>151927</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>262</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>175303</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>175303</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>175303</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>48848</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>40281</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>58282</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>36,77%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>30,32%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>43,87%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>39112</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>31178</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>47031</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>31470</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>47159</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>33,56%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>26,75%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>40,35%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>48848</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>40131</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>58334</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>36,77%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>27,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>43,91%</t>
+          <t>40,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>76543</t>
+          <t>75884</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>99679</t>
+          <t>99148</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>39,97%</t>
+          <t>39,75%</t>
         </is>
       </c>
     </row>
@@ -5416,72 +5416,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>83999</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>74565</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>92566</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>63,23%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>56,13%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>69,68%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>130</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>77440</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>69521</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>85374</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>69393</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>85082</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>66,44%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>59,65%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>73,25%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>83999</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>74513</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>92716</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>63,23%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>56,09%</t>
+          <t>59,54%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>69,79%</t>
+          <t>73,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>149720</t>
+          <t>150251</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>172856</t>
+          <t>173515</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>60,03%</t>
+          <t>60,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>69,31%</t>
+          <t>69,57%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>132847</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>132847</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>132847</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>195</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>116552</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>116552</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>116552</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>132847</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>132847</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>132847</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,72 +5646,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>53114</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>43582</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>64086</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>33,57%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>27,55%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>40,51%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>77</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>58286</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>48282</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>68851</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>48125</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>68384</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>34,94%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>28,94%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>41,27%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>53114</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>42730</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>62308</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>33,57%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>39,38%</t>
+          <t>40,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>97887</t>
+          <t>96454</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>125643</t>
+          <t>124731</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>29,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,66%</t>
+          <t>38,37%</t>
         </is>
       </c>
     </row>
@@ -5759,72 +5759,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>105094</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>94122</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>114626</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>66,43%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>59,49%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>72,45%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>147</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>108541</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>97976</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>118545</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>98443</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>118702</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>65,06%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>58,73%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>71,06%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>152</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>105094</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>95900</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>115478</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>66,43%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>60,62%</t>
+          <t>59,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,99%</t>
+          <t>71,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>199392</t>
+          <t>200304</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>227148</t>
+          <t>228581</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>61,34%</t>
+          <t>61,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,88%</t>
+          <t>70,33%</t>
         </is>
       </c>
     </row>
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>158208</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>158208</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>158208</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>224</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>166827</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>166827</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>166827</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>226</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>158208</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>158208</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>158208</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,72 +5989,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>188932</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>170425</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>208535</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>33,09%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>29,84%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>36,52%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>253</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>170985</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>154519</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>189234</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>152883</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>188892</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>32,54%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>29,41%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>36,02%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>268</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>188932</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>171223</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>207722</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>33,09%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>29,98%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>35,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>334332</t>
+          <t>333384</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>382916</t>
+          <t>386607</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>34,92%</t>
+          <t>35,26%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>557</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>382101</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>362498</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>400608</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>66,91%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>63,48%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>70,16%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>537</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>354405</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>336156</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>370871</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>336498</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>372507</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>67,46%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>63,98%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>70,59%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>557</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>382101</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>363311</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>399810</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>66,91%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>63,62%</t>
+          <t>64,05%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>70,02%</t>
+          <t>70,9%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>713507</t>
+          <t>709816</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>762091</t>
+          <t>763039</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>65,08%</t>
+          <t>64,74%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,51%</t>
+          <t>69,59%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>825</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>571033</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>571033</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>571033</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>790</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>525390</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>525390</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>525390</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>825</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>571033</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>571033</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>571033</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,72 +6564,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>116020</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>109284</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>120230</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>92,15%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>86,8%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>95,49%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>175</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>104795</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>98534</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>109496</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>89,35%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>84,02%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>93,36%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>156</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>129701</t>
+          <t>108634</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>122534</t>
+          <t>102481</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>134651</t>
+          <t>113337</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>89,73%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>87,27%</t>
+          <t>84,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>234497</t>
+          <t>224654</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>225502</t>
+          <t>216354</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>241625</t>
+          <t>231848</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>90,96%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>87,51%</t>
+          <t>87,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,87%</t>
         </is>
       </c>
     </row>
@@ -6677,72 +6677,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>9886</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>5676</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>16622</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>7,85%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>4,51%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>13,2%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>12485</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>7784</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>18746</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>10,65%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>6,64%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>15,98%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10711</t>
+          <t>12437</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5761</t>
+          <t>7734</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17878</t>
+          <t>18590</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>23196</t>
+          <t>22323</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>16068</t>
+          <t>15129</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>32191</t>
+          <t>30623</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,4%</t>
         </is>
       </c>
     </row>
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>196</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>257693</t>
+          <t>246977</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>257693</t>
+          <t>246977</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>257693</t>
+          <t>246977</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>287</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>196710</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>185282</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>206710</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>82,93%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>78,11%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>87,14%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>245</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>161845</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>144370</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>170818</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>84,95%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>75,78%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>89,66%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>287</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>212055</t>
+          <t>160697</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>199003</t>
+          <t>151192</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>221945</t>
+          <t>167218</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>83,15%</t>
+          <t>87,14%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>78,03%</t>
+          <t>81,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>87,03%</t>
+          <t>90,68%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>373901</t>
+          <t>357407</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>353384</t>
+          <t>343028</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>389102</t>
+          <t>368841</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>83,92%</t>
+          <t>84,77%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>79,31%</t>
+          <t>81,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>87,48%</t>
         </is>
       </c>
     </row>
@@ -7020,72 +7020,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>40496</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>30496</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>51924</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>17,07%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>12,86%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>21,89%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>28667</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>19694</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>46142</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>15,05%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>10,34%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>24,22%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>42980</t>
+          <t>23716</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>33090</t>
+          <t>17195</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>56032</t>
+          <t>33221</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>71647</t>
+          <t>64212</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>56446</t>
+          <t>52778</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>92164</t>
+          <t>78591</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>18,64%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>343</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>237206</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>237206</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>237206</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>280</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>190512</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>190512</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>190512</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>343</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>255035</t>
+          <t>184413</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>255035</t>
+          <t>184413</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>255035</t>
+          <t>184413</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>445548</t>
+          <t>421619</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>445548</t>
+          <t>421619</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>445548</t>
+          <t>421619</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>146044</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>137123</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>153176</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>86,75%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>81,46%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>90,99%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>200</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>170294</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>158788</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>179542</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>89,44%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>83,4%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>94,3%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>161107</t>
+          <t>139564</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>151654</t>
+          <t>131908</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>168248</t>
+          <t>145486</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>86,95%</t>
+          <t>88,87%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>81,85%</t>
+          <t>83,99%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>92,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>331401</t>
+          <t>285607</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>318088</t>
+          <t>274199</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>344343</t>
+          <t>295863</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>88,21%</t>
+          <t>87,77%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>84,67%</t>
+          <t>84,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>90,93%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>22297</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>15165</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>31218</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>13,25%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>9,01%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>18,54%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>20107</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>10859</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>31613</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>10,56%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>5,7%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>16,6%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>24179</t>
+          <t>17486</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17038</t>
+          <t>11564</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>33632</t>
+          <t>25142</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>44286</t>
+          <t>39784</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>31344</t>
+          <t>29528</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>57599</t>
+          <t>51192</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,73%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>168341</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>168341</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>168341</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>227</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>190401</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>190401</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>190401</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>157050</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>157050</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>157050</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>375687</t>
+          <t>325391</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>375687</t>
+          <t>325391</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>375687</t>
+          <t>325391</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>143092</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>134652</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>150486</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>84,48%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>79,5%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>88,85%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>196</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>134631</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>124909</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>143132</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>80,16%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>74,37%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>85,22%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>153751</t>
+          <t>136056</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>143591</t>
+          <t>126615</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>161390</t>
+          <t>143766</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>81,4%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>79,23%</t>
+          <t>75,75%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>89,05%</t>
+          <t>86,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>288383</t>
+          <t>279147</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>275701</t>
+          <t>265343</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>300775</t>
+          <t>289257</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>82,58%</t>
+          <t>82,95%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>78,95%</t>
+          <t>78,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>86,13%</t>
+          <t>85,96%</t>
         </is>
       </c>
     </row>
@@ -7706,72 +7706,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>26284</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>18890</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>34724</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>15,52%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>11,15%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>20,5%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>33331</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>24830</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>43053</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>19,84%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>14,78%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>25,63%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>27487</t>
+          <t>31089</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>19848</t>
+          <t>23379</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>37647</t>
+          <t>40530</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>60818</t>
+          <t>57374</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>48426</t>
+          <t>47264</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>73500</t>
+          <t>71178</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>21,15%</t>
         </is>
       </c>
     </row>
@@ -7819,57 +7819,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>169376</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>169376</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>169376</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>240</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>167962</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>167962</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>167962</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>238</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>181238</t>
+          <t>167145</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>181238</t>
+          <t>167145</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>181238</t>
+          <t>167145</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>349201</t>
+          <t>336521</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>349201</t>
+          <t>336521</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>349201</t>
+          <t>336521</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>839</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>601865</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>583378</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>616585</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>85,88%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>83,24%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>87,98%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>816</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>571565</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>549921</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>590002</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>85,8%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>82,55%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>88,57%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>839</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>656615</t>
+          <t>544949</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>637030</t>
+          <t>529290</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>673605</t>
+          <t>559406</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>86,17%</t>
+          <t>86,54%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>83,6%</t>
+          <t>84,06%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>88,4%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1228181</t>
+          <t>1146816</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1200986</t>
+          <t>1124354</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1252460</t>
+          <t>1167240</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>86,0%</t>
+          <t>86,19%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>84,1%</t>
+          <t>84,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>87,73%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>98964</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>84244</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>117451</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>14,12%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>12,02%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>16,76%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>127</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>94590</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>76153</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>116234</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>14,2%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>11,43%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>17,45%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>105357</t>
+          <t>84729</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>88367</t>
+          <t>70272</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>124942</t>
+          <t>100388</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>199946</t>
+          <t>183692</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>175667</t>
+          <t>163268</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>227141</t>
+          <t>206154</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,49%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>977</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>943</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>666155</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>666155</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>666155</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>977</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>629678</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>629678</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>629678</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1428127</t>
+          <t>1330508</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1428127</t>
+          <t>1330508</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1428127</t>
+          <t>1330508</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
